--- a/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v3/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v3/Contrary(P)Body(N).xlsx
@@ -30681,16 +30681,16 @@
         <v>126</v>
       </c>
       <c r="L2" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M2" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
     <row r="3">
@@ -30740,16 +30740,16 @@
         <v>126</v>
       </c>
       <c r="L3" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M3" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
     <row r="4">
@@ -30799,16 +30799,16 @@
         <v>126</v>
       </c>
       <c r="L4" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M4" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
   </sheetData>
